--- a/models/demo-hwp101/demo-hwp101.xlsx
+++ b/models/demo-hwp101/demo-hwp101.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/demo-hwp101/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-hwp101/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5D1A8D-7685-EE49-97E0-A9FD8CFB6E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F56524C-0243-114F-BC75-4D3510AD4644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26980" activeTab="1" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19320" activeTab="1" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Inputs - Spatial" sheetId="4" r:id="rId4"/>
     <sheet name="Inputs - Advanced Curves" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,6 +44,7 @@
   <authors>
     <author>Magnan, Michael</author>
     <author>mhafer</author>
+    <author>tc={91195192-5E6A-034F-99E5-92DF8ABA3078}</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{DE5AEED7-5306-0F41-A9F6-E09723C07087}">
@@ -398,27 +399,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G52" authorId="0" shapeId="0" xr:uid="{9D0C205B-9C9C-3F4A-912F-B707A4FF980A}">
+    <comment ref="G52" authorId="2" shapeId="0" xr:uid="{91195192-5E6A-034F-99E5-92DF8ABA3078}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -775,7 +762,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="128">
   <si>
     <t>Keyword: POOL</t>
   </si>
@@ -888,18 +875,9 @@
     <t>Proportion</t>
   </si>
   <si>
-    <t>Target Amount (Double precison)</t>
-  </si>
-  <si>
     <t>New Physical State Name</t>
   </si>
   <si>
-    <t>Filter By Physical State Name/Group</t>
-  </si>
-  <si>
-    <t>Filter By Species Name/Group</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -1161,7 +1139,13 @@
     <t>Exponential Decay 35</t>
   </si>
   <si>
-    <t>COMMENT</t>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Physical State Rule</t>
+  </si>
+  <si>
+    <t>Species Rule</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1153,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -1215,7 +1199,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1226,6 +1210,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1241,12 +1231,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1283,6 +1274,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Magnan, Michael" id="{360EC44D-784E-7443-9DE2-170B1B1751FB}" userId="" providerId=""/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1600,6 +1597,15 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G52" personId="{360EC44D-784E-7443-9DE2-170B1B1751FB}" id="{91195192-5E6A-034F-99E5-92DF8ABA3078}">
+    <text xml:space="preserve">The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
   <dimension ref="B1:L60"/>
@@ -1754,10 +1760,10 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
@@ -1818,7 +1824,7 @@
         <v>Combusting, Shengs Lumber</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E15">
         <f>'Inputs - Spatial'!$C$3</f>
@@ -1869,26 +1875,26 @@
     </row>
     <row r="22" spans="2:7" ht="16" customHeight="1">
       <c r="B22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="16" customHeight="1">
       <c r="B23" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="16" customHeight="1">
       <c r="B24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
@@ -2153,7 +2159,7 @@
         <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>30</v>
@@ -2201,7 +2207,7 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D50" t="str">
         <f>C24</f>
@@ -2224,25 +2230,25 @@
       <c r="E52" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="16" customHeight="1">
       <c r="B54" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C54" t="str">
         <f>$C$48</f>
@@ -2258,7 +2264,7 @@
     </row>
     <row r="55" spans="2:10" ht="16" customHeight="1">
       <c r="B55" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" ref="C55" si="0">$C$48</f>
@@ -2274,7 +2280,7 @@
     </row>
     <row r="57" spans="2:10" ht="16" customHeight="1">
       <c r="B57" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C57" t="str">
         <f>C49</f>
@@ -2290,7 +2296,7 @@
     </row>
     <row r="58" spans="2:10" ht="16" customHeight="1">
       <c r="B58" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C58" t="str">
         <f>C49</f>
@@ -2306,7 +2312,7 @@
     </row>
     <row r="60" spans="2:10" ht="16" customHeight="1">
       <c r="B60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C60" t="str">
         <f>C50</f>
@@ -2328,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22152807-D21A-1A49-9C05-E8FAC8B5CEA8}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="B1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2341,41 +2347,41 @@
     <col min="11" max="11" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
+    <row r="1" spans="2:11" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2392,12 +2398,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>128</v>
-      </c>
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2414,12 +2417,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>128</v>
-      </c>
+    <row r="5" spans="2:11">
       <c r="B5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2436,12 +2436,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>128</v>
-      </c>
+    <row r="6" spans="2:11">
       <c r="B6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C6" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2480,58 +2477,58 @@
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1">
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1</v>
@@ -2545,27 +2542,27 @@
     </row>
     <row r="11" spans="2:7" s="3" customFormat="1">
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="2:7" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>30</v>
@@ -2576,23 +2573,23 @@
     </row>
     <row r="15" spans="2:7">
       <c r="B15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="2:5" s="3" customFormat="1">
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>1</v>
@@ -2606,24 +2603,24 @@
     </row>
     <row r="20" spans="2:5" s="3" customFormat="1">
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="2:5" s="3" customFormat="1">
       <c r="B22" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>31</v>
@@ -2653,22 +2650,22 @@
   <sheetData>
     <row r="1" spans="2:8" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>31</v>
@@ -2676,7 +2673,7 @@
     </row>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>9693</v>
@@ -2691,7 +2688,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>558</v>
@@ -2706,7 +2703,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>778</v>
@@ -2721,13 +2718,13 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>999</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2735,7 +2732,7 @@
     </row>
     <row r="8" spans="2:8" s="3" customFormat="1">
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1</v>
@@ -2743,29 +2740,29 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:8" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>31</v>
@@ -2773,10 +2770,10 @@
     </row>
     <row r="15" spans="2:8">
       <c r="B15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D15" t="str">
         <f>C10</f>
@@ -2785,10 +2782,10 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D16" t="str">
         <f>C10</f>
@@ -2797,10 +2794,10 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D17" t="str">
         <f>C11</f>
@@ -2809,10 +2806,10 @@
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D18" t="str">
         <f>C11</f>
@@ -2821,10 +2818,10 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D19" t="str">
         <f>C11</f>
@@ -2833,24 +2830,24 @@
     </row>
     <row r="21" spans="2:5" s="3" customFormat="1">
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E23" t="str">
         <f>C17</f>
@@ -2859,7 +2856,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C24" t="str">
         <f>C15</f>
@@ -2872,7 +2869,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C25" t="str">
         <f>C16</f>
@@ -2885,7 +2882,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C26" t="str">
         <f>C17</f>
@@ -2898,7 +2895,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C27" t="str">
         <f>C18</f>
@@ -2911,7 +2908,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C28" t="str">
         <f>C19</f>
@@ -2943,13 +2940,13 @@
   <sheetData>
     <row r="1" spans="2:6" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>30</v>
@@ -2960,29 +2957,29 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="2:6" s="3" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
@@ -2996,40 +2993,40 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="2:6" s="3" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C14" t="str">
         <f>C9</f>
@@ -3048,7 +3045,7 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C15" t="str">
         <f>C10</f>
@@ -3067,21 +3064,21 @@
     </row>
     <row r="19" spans="2:5" s="3" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C21" t="str">
         <f>C4</f>
@@ -3097,7 +3094,7 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C22" t="str">
         <f>C4</f>
@@ -3113,7 +3110,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C24" t="str">
         <f>$C$3</f>
@@ -3128,7 +3125,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" ref="C25:C88" si="0">$C$3</f>
@@ -3143,7 +3140,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -3158,7 +3155,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -3173,7 +3170,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -3188,7 +3185,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -3203,7 +3200,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -3218,7 +3215,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -3233,7 +3230,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -3248,7 +3245,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -3263,7 +3260,7 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -3278,7 +3275,7 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -3293,7 +3290,7 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -3308,7 +3305,7 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -3323,7 +3320,7 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -3338,7 +3335,7 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -3353,7 +3350,7 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -3368,7 +3365,7 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -3383,7 +3380,7 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
@@ -3398,7 +3395,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
@@ -3413,7 +3410,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
@@ -3428,7 +3425,7 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
@@ -3443,7 +3440,7 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
@@ -3458,7 +3455,7 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
@@ -3473,7 +3470,7 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
@@ -3488,7 +3485,7 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
@@ -3503,7 +3500,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
@@ -3518,7 +3515,7 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
@@ -3533,7 +3530,7 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
@@ -3548,7 +3545,7 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
@@ -3563,7 +3560,7 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -3578,7 +3575,7 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -3593,7 +3590,7 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -3608,7 +3605,7 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -3623,7 +3620,7 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -3638,7 +3635,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
@@ -3653,7 +3650,7 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
@@ -3668,7 +3665,7 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
@@ -3683,7 +3680,7 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
@@ -3698,7 +3695,7 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
@@ -3713,7 +3710,7 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
@@ -3728,7 +3725,7 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="0"/>
@@ -3743,7 +3740,7 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="0"/>
@@ -3758,7 +3755,7 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="0"/>
@@ -3773,7 +3770,7 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="0"/>
@@ -3788,7 +3785,7 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="0"/>
@@ -3803,7 +3800,7 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="0"/>
@@ -3818,7 +3815,7 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="0"/>
@@ -3833,7 +3830,7 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="0"/>
@@ -3848,7 +3845,7 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="0"/>
@@ -3863,7 +3860,7 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="0"/>
@@ -3878,7 +3875,7 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="0"/>
@@ -3893,7 +3890,7 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="0"/>
@@ -3908,7 +3905,7 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="0"/>
@@ -3923,7 +3920,7 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="0"/>
@@ -3938,7 +3935,7 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="0"/>
@@ -3953,7 +3950,7 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="0"/>
@@ -3968,7 +3965,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="0"/>
@@ -3983,7 +3980,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="0"/>
@@ -3998,7 +3995,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="0"/>
@@ -4013,7 +4010,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="0"/>
@@ -4028,7 +4025,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="0"/>
@@ -4043,7 +4040,7 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="0"/>
@@ -4058,7 +4055,7 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="0"/>
@@ -4073,7 +4070,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="0"/>
@@ -4088,7 +4085,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" ref="C89:C152" si="1">$C$3</f>
@@ -4103,7 +4100,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
@@ -4118,7 +4115,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
@@ -4133,7 +4130,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
@@ -4148,7 +4145,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
@@ -4163,7 +4160,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
@@ -4178,7 +4175,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
@@ -4193,7 +4190,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
@@ -4208,7 +4205,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
@@ -4223,7 +4220,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
@@ -4238,7 +4235,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
@@ -4253,7 +4250,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
@@ -4268,7 +4265,7 @@
     </row>
     <row r="101" spans="2:5">
       <c r="B101" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
@@ -4283,7 +4280,7 @@
     </row>
     <row r="102" spans="2:5">
       <c r="B102" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
@@ -4298,7 +4295,7 @@
     </row>
     <row r="103" spans="2:5">
       <c r="B103" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
@@ -4313,7 +4310,7 @@
     </row>
     <row r="104" spans="2:5">
       <c r="B104" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
@@ -4328,7 +4325,7 @@
     </row>
     <row r="105" spans="2:5">
       <c r="B105" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
@@ -4343,7 +4340,7 @@
     </row>
     <row r="106" spans="2:5">
       <c r="B106" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
@@ -4358,7 +4355,7 @@
     </row>
     <row r="107" spans="2:5">
       <c r="B107" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
@@ -4373,7 +4370,7 @@
     </row>
     <row r="108" spans="2:5">
       <c r="B108" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
@@ -4388,7 +4385,7 @@
     </row>
     <row r="109" spans="2:5">
       <c r="B109" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
@@ -4403,7 +4400,7 @@
     </row>
     <row r="110" spans="2:5">
       <c r="B110" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
@@ -4418,7 +4415,7 @@
     </row>
     <row r="111" spans="2:5">
       <c r="B111" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
@@ -4433,7 +4430,7 @@
     </row>
     <row r="112" spans="2:5">
       <c r="B112" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
@@ -4448,7 +4445,7 @@
     </row>
     <row r="113" spans="2:5">
       <c r="B113" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
@@ -4463,7 +4460,7 @@
     </row>
     <row r="114" spans="2:5">
       <c r="B114" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
@@ -4478,7 +4475,7 @@
     </row>
     <row r="115" spans="2:5">
       <c r="B115" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
@@ -4493,7 +4490,7 @@
     </row>
     <row r="116" spans="2:5">
       <c r="B116" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
@@ -4508,7 +4505,7 @@
     </row>
     <row r="117" spans="2:5">
       <c r="B117" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
@@ -4523,7 +4520,7 @@
     </row>
     <row r="118" spans="2:5">
       <c r="B118" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="119" spans="2:5">
       <c r="B119" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
@@ -4553,7 +4550,7 @@
     </row>
     <row r="120" spans="2:5">
       <c r="B120" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
@@ -4568,7 +4565,7 @@
     </row>
     <row r="121" spans="2:5">
       <c r="B121" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
@@ -4583,7 +4580,7 @@
     </row>
     <row r="122" spans="2:5">
       <c r="B122" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
@@ -4598,7 +4595,7 @@
     </row>
     <row r="123" spans="2:5">
       <c r="B123" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
@@ -4613,7 +4610,7 @@
     </row>
     <row r="124" spans="2:5">
       <c r="B124" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
@@ -4628,7 +4625,7 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
@@ -4643,7 +4640,7 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
@@ -4658,7 +4655,7 @@
     </row>
     <row r="127" spans="2:5">
       <c r="B127" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
@@ -4673,7 +4670,7 @@
     </row>
     <row r="128" spans="2:5">
       <c r="B128" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
@@ -4688,7 +4685,7 @@
     </row>
     <row r="129" spans="2:5">
       <c r="B129" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="1"/>
@@ -4703,7 +4700,7 @@
     </row>
     <row r="130" spans="2:5">
       <c r="B130" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="1"/>
@@ -4718,7 +4715,7 @@
     </row>
     <row r="131" spans="2:5">
       <c r="B131" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="1"/>
@@ -4733,7 +4730,7 @@
     </row>
     <row r="132" spans="2:5">
       <c r="B132" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="1"/>
@@ -4748,7 +4745,7 @@
     </row>
     <row r="133" spans="2:5">
       <c r="B133" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="1"/>
@@ -4763,7 +4760,7 @@
     </row>
     <row r="134" spans="2:5">
       <c r="B134" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="1"/>
@@ -4778,7 +4775,7 @@
     </row>
     <row r="135" spans="2:5">
       <c r="B135" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="1"/>
@@ -4793,7 +4790,7 @@
     </row>
     <row r="136" spans="2:5">
       <c r="B136" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="1"/>
@@ -4808,7 +4805,7 @@
     </row>
     <row r="137" spans="2:5">
       <c r="B137" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="1"/>
@@ -4823,7 +4820,7 @@
     </row>
     <row r="138" spans="2:5">
       <c r="B138" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="1"/>
@@ -4838,7 +4835,7 @@
     </row>
     <row r="139" spans="2:5">
       <c r="B139" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="1"/>
@@ -4853,7 +4850,7 @@
     </row>
     <row r="140" spans="2:5">
       <c r="B140" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="1"/>
@@ -4868,7 +4865,7 @@
     </row>
     <row r="141" spans="2:5">
       <c r="B141" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="1"/>
@@ -4883,7 +4880,7 @@
     </row>
     <row r="142" spans="2:5">
       <c r="B142" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="1"/>
@@ -4898,7 +4895,7 @@
     </row>
     <row r="143" spans="2:5">
       <c r="B143" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="1"/>
@@ -4913,7 +4910,7 @@
     </row>
     <row r="144" spans="2:5">
       <c r="B144" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C144" t="str">
         <f t="shared" si="1"/>
@@ -4928,7 +4925,7 @@
     </row>
     <row r="145" spans="2:5">
       <c r="B145" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C145" t="str">
         <f t="shared" si="1"/>
@@ -4943,7 +4940,7 @@
     </row>
     <row r="146" spans="2:5">
       <c r="B146" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C146" t="str">
         <f t="shared" si="1"/>
@@ -4958,7 +4955,7 @@
     </row>
     <row r="147" spans="2:5">
       <c r="B147" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C147" t="str">
         <f t="shared" si="1"/>
@@ -4973,7 +4970,7 @@
     </row>
     <row r="148" spans="2:5">
       <c r="B148" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C148" t="str">
         <f t="shared" si="1"/>
@@ -4988,7 +4985,7 @@
     </row>
     <row r="149" spans="2:5">
       <c r="B149" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C149" t="str">
         <f t="shared" si="1"/>
@@ -5003,7 +5000,7 @@
     </row>
     <row r="150" spans="2:5">
       <c r="B150" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C150" t="str">
         <f t="shared" si="1"/>
@@ -5018,7 +5015,7 @@
     </row>
     <row r="151" spans="2:5">
       <c r="B151" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C151" t="str">
         <f t="shared" si="1"/>
@@ -5033,7 +5030,7 @@
     </row>
     <row r="152" spans="2:5">
       <c r="B152" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C152" t="str">
         <f t="shared" si="1"/>
@@ -5048,7 +5045,7 @@
     </row>
     <row r="153" spans="2:5">
       <c r="B153" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C153" t="str">
         <f t="shared" ref="C153:C216" si="2">$C$3</f>
@@ -5063,7 +5060,7 @@
     </row>
     <row r="154" spans="2:5">
       <c r="B154" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C154" t="str">
         <f t="shared" si="2"/>
@@ -5078,7 +5075,7 @@
     </row>
     <row r="155" spans="2:5">
       <c r="B155" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C155" t="str">
         <f t="shared" si="2"/>
@@ -5093,7 +5090,7 @@
     </row>
     <row r="156" spans="2:5">
       <c r="B156" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C156" t="str">
         <f t="shared" si="2"/>
@@ -5108,7 +5105,7 @@
     </row>
     <row r="157" spans="2:5">
       <c r="B157" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C157" t="str">
         <f t="shared" si="2"/>
@@ -5123,7 +5120,7 @@
     </row>
     <row r="158" spans="2:5">
       <c r="B158" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C158" t="str">
         <f t="shared" si="2"/>
@@ -5138,7 +5135,7 @@
     </row>
     <row r="159" spans="2:5">
       <c r="B159" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C159" t="str">
         <f t="shared" si="2"/>
@@ -5153,7 +5150,7 @@
     </row>
     <row r="160" spans="2:5">
       <c r="B160" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C160" t="str">
         <f t="shared" si="2"/>
@@ -5168,7 +5165,7 @@
     </row>
     <row r="161" spans="2:5">
       <c r="B161" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C161" t="str">
         <f t="shared" si="2"/>
@@ -5183,7 +5180,7 @@
     </row>
     <row r="162" spans="2:5">
       <c r="B162" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C162" t="str">
         <f t="shared" si="2"/>
@@ -5198,7 +5195,7 @@
     </row>
     <row r="163" spans="2:5">
       <c r="B163" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C163" t="str">
         <f t="shared" si="2"/>
@@ -5213,7 +5210,7 @@
     </row>
     <row r="164" spans="2:5">
       <c r="B164" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C164" t="str">
         <f t="shared" si="2"/>
@@ -5228,7 +5225,7 @@
     </row>
     <row r="165" spans="2:5">
       <c r="B165" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C165" t="str">
         <f t="shared" si="2"/>
@@ -5243,7 +5240,7 @@
     </row>
     <row r="166" spans="2:5">
       <c r="B166" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C166" t="str">
         <f t="shared" si="2"/>
@@ -5258,7 +5255,7 @@
     </row>
     <row r="167" spans="2:5">
       <c r="B167" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C167" t="str">
         <f t="shared" si="2"/>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="168" spans="2:5">
       <c r="B168" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C168" t="str">
         <f t="shared" si="2"/>
@@ -5288,7 +5285,7 @@
     </row>
     <row r="169" spans="2:5">
       <c r="B169" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C169" t="str">
         <f t="shared" si="2"/>
@@ -5303,7 +5300,7 @@
     </row>
     <row r="170" spans="2:5">
       <c r="B170" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C170" t="str">
         <f t="shared" si="2"/>
@@ -5318,7 +5315,7 @@
     </row>
     <row r="171" spans="2:5">
       <c r="B171" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C171" t="str">
         <f t="shared" si="2"/>
@@ -5333,7 +5330,7 @@
     </row>
     <row r="172" spans="2:5">
       <c r="B172" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C172" t="str">
         <f t="shared" si="2"/>
@@ -5348,7 +5345,7 @@
     </row>
     <row r="173" spans="2:5">
       <c r="B173" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C173" t="str">
         <f t="shared" si="2"/>
@@ -5363,7 +5360,7 @@
     </row>
     <row r="174" spans="2:5">
       <c r="B174" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C174" t="str">
         <f t="shared" si="2"/>
@@ -5378,7 +5375,7 @@
     </row>
     <row r="175" spans="2:5">
       <c r="B175" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="2"/>
@@ -5393,7 +5390,7 @@
     </row>
     <row r="176" spans="2:5">
       <c r="B176" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="2"/>
@@ -5408,7 +5405,7 @@
     </row>
     <row r="177" spans="2:5">
       <c r="B177" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="2"/>
@@ -5423,7 +5420,7 @@
     </row>
     <row r="178" spans="2:5">
       <c r="B178" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C178" t="str">
         <f t="shared" si="2"/>
@@ -5438,7 +5435,7 @@
     </row>
     <row r="179" spans="2:5">
       <c r="B179" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C179" t="str">
         <f t="shared" si="2"/>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="180" spans="2:5">
       <c r="B180" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="2"/>
@@ -5468,7 +5465,7 @@
     </row>
     <row r="181" spans="2:5">
       <c r="B181" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C181" t="str">
         <f t="shared" si="2"/>
@@ -5483,7 +5480,7 @@
     </row>
     <row r="182" spans="2:5">
       <c r="B182" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C182" t="str">
         <f t="shared" si="2"/>
@@ -5498,7 +5495,7 @@
     </row>
     <row r="183" spans="2:5">
       <c r="B183" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C183" t="str">
         <f t="shared" si="2"/>
@@ -5513,7 +5510,7 @@
     </row>
     <row r="184" spans="2:5">
       <c r="B184" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="2"/>
@@ -5528,7 +5525,7 @@
     </row>
     <row r="185" spans="2:5">
       <c r="B185" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C185" t="str">
         <f t="shared" si="2"/>
@@ -5543,7 +5540,7 @@
     </row>
     <row r="186" spans="2:5">
       <c r="B186" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C186" t="str">
         <f t="shared" si="2"/>
@@ -5558,7 +5555,7 @@
     </row>
     <row r="187" spans="2:5">
       <c r="B187" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="2"/>
@@ -5573,7 +5570,7 @@
     </row>
     <row r="188" spans="2:5">
       <c r="B188" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="2"/>
@@ -5588,7 +5585,7 @@
     </row>
     <row r="189" spans="2:5">
       <c r="B189" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C189" t="str">
         <f t="shared" si="2"/>
@@ -5603,7 +5600,7 @@
     </row>
     <row r="190" spans="2:5">
       <c r="B190" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C190" t="str">
         <f t="shared" si="2"/>
@@ -5618,7 +5615,7 @@
     </row>
     <row r="191" spans="2:5">
       <c r="B191" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C191" t="str">
         <f t="shared" si="2"/>
@@ -5633,7 +5630,7 @@
     </row>
     <row r="192" spans="2:5">
       <c r="B192" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C192" t="str">
         <f t="shared" si="2"/>
@@ -5648,7 +5645,7 @@
     </row>
     <row r="193" spans="2:5">
       <c r="B193" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C193" t="str">
         <f t="shared" si="2"/>
@@ -5663,7 +5660,7 @@
     </row>
     <row r="194" spans="2:5">
       <c r="B194" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C194" t="str">
         <f t="shared" si="2"/>
@@ -5678,7 +5675,7 @@
     </row>
     <row r="195" spans="2:5">
       <c r="B195" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C195" t="str">
         <f t="shared" si="2"/>
@@ -5693,7 +5690,7 @@
     </row>
     <row r="196" spans="2:5">
       <c r="B196" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C196" t="str">
         <f t="shared" si="2"/>
@@ -5708,7 +5705,7 @@
     </row>
     <row r="197" spans="2:5">
       <c r="B197" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C197" t="str">
         <f t="shared" si="2"/>
@@ -5723,7 +5720,7 @@
     </row>
     <row r="198" spans="2:5">
       <c r="B198" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C198" t="str">
         <f t="shared" si="2"/>
@@ -5738,7 +5735,7 @@
     </row>
     <row r="199" spans="2:5">
       <c r="B199" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C199" t="str">
         <f t="shared" si="2"/>
@@ -5753,7 +5750,7 @@
     </row>
     <row r="200" spans="2:5">
       <c r="B200" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C200" t="str">
         <f t="shared" si="2"/>
@@ -5768,7 +5765,7 @@
     </row>
     <row r="201" spans="2:5">
       <c r="B201" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C201" t="str">
         <f t="shared" si="2"/>
@@ -5783,7 +5780,7 @@
     </row>
     <row r="202" spans="2:5">
       <c r="B202" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C202" t="str">
         <f t="shared" si="2"/>
@@ -5798,7 +5795,7 @@
     </row>
     <row r="203" spans="2:5">
       <c r="B203" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C203" t="str">
         <f t="shared" si="2"/>
@@ -5813,7 +5810,7 @@
     </row>
     <row r="204" spans="2:5">
       <c r="B204" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C204" t="str">
         <f t="shared" si="2"/>
@@ -5828,7 +5825,7 @@
     </row>
     <row r="205" spans="2:5">
       <c r="B205" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C205" t="str">
         <f t="shared" si="2"/>
@@ -5843,7 +5840,7 @@
     </row>
     <row r="206" spans="2:5">
       <c r="B206" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C206" t="str">
         <f t="shared" si="2"/>
@@ -5858,7 +5855,7 @@
     </row>
     <row r="207" spans="2:5">
       <c r="B207" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C207" t="str">
         <f t="shared" si="2"/>
@@ -5873,7 +5870,7 @@
     </row>
     <row r="208" spans="2:5">
       <c r="B208" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C208" t="str">
         <f t="shared" si="2"/>
@@ -5888,7 +5885,7 @@
     </row>
     <row r="209" spans="2:5">
       <c r="B209" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C209" t="str">
         <f t="shared" si="2"/>
@@ -5903,7 +5900,7 @@
     </row>
     <row r="210" spans="2:5">
       <c r="B210" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C210" t="str">
         <f t="shared" si="2"/>
@@ -5918,7 +5915,7 @@
     </row>
     <row r="211" spans="2:5">
       <c r="B211" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C211" t="str">
         <f t="shared" si="2"/>
@@ -5933,7 +5930,7 @@
     </row>
     <row r="212" spans="2:5">
       <c r="B212" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C212" t="str">
         <f t="shared" si="2"/>
@@ -5948,7 +5945,7 @@
     </row>
     <row r="213" spans="2:5">
       <c r="B213" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C213" t="str">
         <f t="shared" si="2"/>
@@ -5963,7 +5960,7 @@
     </row>
     <row r="214" spans="2:5">
       <c r="B214" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C214" t="str">
         <f t="shared" si="2"/>
@@ -5978,7 +5975,7 @@
     </row>
     <row r="215" spans="2:5">
       <c r="B215" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C215" t="str">
         <f t="shared" si="2"/>
@@ -5993,7 +5990,7 @@
     </row>
     <row r="216" spans="2:5">
       <c r="B216" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C216" t="str">
         <f t="shared" si="2"/>
@@ -6008,7 +6005,7 @@
     </row>
     <row r="217" spans="2:5">
       <c r="B217" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C217" t="str">
         <f t="shared" ref="C217:C280" si="3">$C$3</f>
@@ -6023,7 +6020,7 @@
     </row>
     <row r="218" spans="2:5">
       <c r="B218" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C218" t="str">
         <f t="shared" si="3"/>
@@ -6038,7 +6035,7 @@
     </row>
     <row r="219" spans="2:5">
       <c r="B219" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C219" t="str">
         <f t="shared" si="3"/>
@@ -6053,7 +6050,7 @@
     </row>
     <row r="220" spans="2:5">
       <c r="B220" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C220" t="str">
         <f t="shared" si="3"/>
@@ -6068,7 +6065,7 @@
     </row>
     <row r="221" spans="2:5">
       <c r="B221" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C221" t="str">
         <f t="shared" si="3"/>
@@ -6083,7 +6080,7 @@
     </row>
     <row r="222" spans="2:5">
       <c r="B222" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C222" t="str">
         <f t="shared" si="3"/>
@@ -6098,7 +6095,7 @@
     </row>
     <row r="223" spans="2:5">
       <c r="B223" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C223" t="str">
         <f t="shared" si="3"/>
@@ -6113,7 +6110,7 @@
     </row>
     <row r="224" spans="2:5">
       <c r="B224" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C224" t="str">
         <f t="shared" si="3"/>
@@ -6128,7 +6125,7 @@
     </row>
     <row r="225" spans="2:5">
       <c r="B225" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C225" t="str">
         <f t="shared" si="3"/>
@@ -6143,7 +6140,7 @@
     </row>
     <row r="226" spans="2:5">
       <c r="B226" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C226" t="str">
         <f t="shared" si="3"/>
@@ -6158,7 +6155,7 @@
     </row>
     <row r="227" spans="2:5">
       <c r="B227" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C227" t="str">
         <f t="shared" si="3"/>
@@ -6173,7 +6170,7 @@
     </row>
     <row r="228" spans="2:5">
       <c r="B228" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C228" t="str">
         <f t="shared" si="3"/>
@@ -6188,7 +6185,7 @@
     </row>
     <row r="229" spans="2:5">
       <c r="B229" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C229" t="str">
         <f t="shared" si="3"/>
@@ -6203,7 +6200,7 @@
     </row>
     <row r="230" spans="2:5">
       <c r="B230" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C230" t="str">
         <f t="shared" si="3"/>
@@ -6218,7 +6215,7 @@
     </row>
     <row r="231" spans="2:5">
       <c r="B231" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C231" t="str">
         <f t="shared" si="3"/>
@@ -6233,7 +6230,7 @@
     </row>
     <row r="232" spans="2:5">
       <c r="B232" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C232" t="str">
         <f t="shared" si="3"/>
@@ -6248,7 +6245,7 @@
     </row>
     <row r="233" spans="2:5">
       <c r="B233" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C233" t="str">
         <f t="shared" si="3"/>
@@ -6263,7 +6260,7 @@
     </row>
     <row r="234" spans="2:5">
       <c r="B234" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C234" t="str">
         <f t="shared" si="3"/>
@@ -6278,7 +6275,7 @@
     </row>
     <row r="235" spans="2:5">
       <c r="B235" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C235" t="str">
         <f t="shared" si="3"/>
@@ -6293,7 +6290,7 @@
     </row>
     <row r="236" spans="2:5">
       <c r="B236" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C236" t="str">
         <f t="shared" si="3"/>
@@ -6308,7 +6305,7 @@
     </row>
     <row r="237" spans="2:5">
       <c r="B237" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C237" t="str">
         <f t="shared" si="3"/>
@@ -6323,7 +6320,7 @@
     </row>
     <row r="238" spans="2:5">
       <c r="B238" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C238" t="str">
         <f t="shared" si="3"/>
@@ -6338,7 +6335,7 @@
     </row>
     <row r="239" spans="2:5">
       <c r="B239" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C239" t="str">
         <f t="shared" si="3"/>
@@ -6353,7 +6350,7 @@
     </row>
     <row r="240" spans="2:5">
       <c r="B240" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C240" t="str">
         <f t="shared" si="3"/>
@@ -6368,7 +6365,7 @@
     </row>
     <row r="241" spans="2:5">
       <c r="B241" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C241" t="str">
         <f t="shared" si="3"/>
@@ -6383,7 +6380,7 @@
     </row>
     <row r="242" spans="2:5">
       <c r="B242" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C242" t="str">
         <f t="shared" si="3"/>
@@ -6398,7 +6395,7 @@
     </row>
     <row r="243" spans="2:5">
       <c r="B243" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C243" t="str">
         <f t="shared" si="3"/>
@@ -6413,7 +6410,7 @@
     </row>
     <row r="244" spans="2:5">
       <c r="B244" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C244" t="str">
         <f t="shared" si="3"/>
@@ -6428,7 +6425,7 @@
     </row>
     <row r="245" spans="2:5">
       <c r="B245" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C245" t="str">
         <f t="shared" si="3"/>
@@ -6443,7 +6440,7 @@
     </row>
     <row r="246" spans="2:5">
       <c r="B246" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C246" t="str">
         <f t="shared" si="3"/>
@@ -6458,7 +6455,7 @@
     </row>
     <row r="247" spans="2:5">
       <c r="B247" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C247" t="str">
         <f t="shared" si="3"/>
@@ -6473,7 +6470,7 @@
     </row>
     <row r="248" spans="2:5">
       <c r="B248" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C248" t="str">
         <f t="shared" si="3"/>
@@ -6488,7 +6485,7 @@
     </row>
     <row r="249" spans="2:5">
       <c r="B249" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C249" t="str">
         <f t="shared" si="3"/>
@@ -6503,7 +6500,7 @@
     </row>
     <row r="250" spans="2:5">
       <c r="B250" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C250" t="str">
         <f t="shared" si="3"/>
@@ -6518,7 +6515,7 @@
     </row>
     <row r="251" spans="2:5">
       <c r="B251" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C251" t="str">
         <f t="shared" si="3"/>
@@ -6533,7 +6530,7 @@
     </row>
     <row r="252" spans="2:5">
       <c r="B252" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C252" t="str">
         <f t="shared" si="3"/>
@@ -6548,7 +6545,7 @@
     </row>
     <row r="253" spans="2:5">
       <c r="B253" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C253" t="str">
         <f t="shared" si="3"/>
@@ -6563,7 +6560,7 @@
     </row>
     <row r="254" spans="2:5">
       <c r="B254" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C254" t="str">
         <f t="shared" si="3"/>
@@ -6578,7 +6575,7 @@
     </row>
     <row r="255" spans="2:5">
       <c r="B255" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C255" t="str">
         <f t="shared" si="3"/>
@@ -6593,7 +6590,7 @@
     </row>
     <row r="256" spans="2:5">
       <c r="B256" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C256" t="str">
         <f t="shared" si="3"/>
@@ -6608,7 +6605,7 @@
     </row>
     <row r="257" spans="2:5">
       <c r="B257" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" si="3"/>
@@ -6623,7 +6620,7 @@
     </row>
     <row r="258" spans="2:5">
       <c r="B258" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C258" t="str">
         <f t="shared" si="3"/>
@@ -6638,7 +6635,7 @@
     </row>
     <row r="259" spans="2:5">
       <c r="B259" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C259" t="str">
         <f t="shared" si="3"/>
@@ -6653,7 +6650,7 @@
     </row>
     <row r="260" spans="2:5">
       <c r="B260" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C260" t="str">
         <f t="shared" si="3"/>
@@ -6668,7 +6665,7 @@
     </row>
     <row r="261" spans="2:5">
       <c r="B261" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C261" t="str">
         <f t="shared" si="3"/>
@@ -6683,7 +6680,7 @@
     </row>
     <row r="262" spans="2:5">
       <c r="B262" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C262" t="str">
         <f t="shared" si="3"/>
@@ -6698,7 +6695,7 @@
     </row>
     <row r="263" spans="2:5">
       <c r="B263" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C263" t="str">
         <f t="shared" si="3"/>
@@ -6713,7 +6710,7 @@
     </row>
     <row r="264" spans="2:5">
       <c r="B264" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C264" t="str">
         <f t="shared" si="3"/>
@@ -6728,7 +6725,7 @@
     </row>
     <row r="265" spans="2:5">
       <c r="B265" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C265" t="str">
         <f t="shared" si="3"/>
@@ -6743,7 +6740,7 @@
     </row>
     <row r="266" spans="2:5">
       <c r="B266" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C266" t="str">
         <f t="shared" si="3"/>
@@ -6758,7 +6755,7 @@
     </row>
     <row r="267" spans="2:5">
       <c r="B267" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C267" t="str">
         <f t="shared" si="3"/>
@@ -6773,7 +6770,7 @@
     </row>
     <row r="268" spans="2:5">
       <c r="B268" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C268" t="str">
         <f t="shared" si="3"/>
@@ -6788,7 +6785,7 @@
     </row>
     <row r="269" spans="2:5">
       <c r="B269" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C269" t="str">
         <f t="shared" si="3"/>
@@ -6803,7 +6800,7 @@
     </row>
     <row r="270" spans="2:5">
       <c r="B270" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C270" t="str">
         <f t="shared" si="3"/>
@@ -6818,7 +6815,7 @@
     </row>
     <row r="271" spans="2:5">
       <c r="B271" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C271" t="str">
         <f t="shared" si="3"/>
@@ -6833,7 +6830,7 @@
     </row>
     <row r="272" spans="2:5">
       <c r="B272" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C272" t="str">
         <f t="shared" si="3"/>
@@ -6848,7 +6845,7 @@
     </row>
     <row r="273" spans="2:5">
       <c r="B273" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C273" t="str">
         <f t="shared" si="3"/>
@@ -6863,7 +6860,7 @@
     </row>
     <row r="274" spans="2:5">
       <c r="B274" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C274" t="str">
         <f t="shared" si="3"/>
@@ -6878,7 +6875,7 @@
     </row>
     <row r="275" spans="2:5">
       <c r="B275" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C275" t="str">
         <f t="shared" si="3"/>
@@ -6893,7 +6890,7 @@
     </row>
     <row r="276" spans="2:5">
       <c r="B276" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C276" t="str">
         <f t="shared" si="3"/>
@@ -6908,7 +6905,7 @@
     </row>
     <row r="277" spans="2:5">
       <c r="B277" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C277" t="str">
         <f t="shared" si="3"/>
@@ -6923,7 +6920,7 @@
     </row>
     <row r="278" spans="2:5">
       <c r="B278" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C278" t="str">
         <f t="shared" si="3"/>
@@ -6938,7 +6935,7 @@
     </row>
     <row r="279" spans="2:5">
       <c r="B279" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C279" t="str">
         <f t="shared" si="3"/>
@@ -6953,7 +6950,7 @@
     </row>
     <row r="280" spans="2:5">
       <c r="B280" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C280" t="str">
         <f t="shared" si="3"/>
@@ -6968,7 +6965,7 @@
     </row>
     <row r="281" spans="2:5">
       <c r="B281" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C281" t="str">
         <f t="shared" ref="C281:C324" si="4">$C$3</f>
@@ -6983,7 +6980,7 @@
     </row>
     <row r="282" spans="2:5">
       <c r="B282" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C282" t="str">
         <f t="shared" si="4"/>
@@ -6998,7 +6995,7 @@
     </row>
     <row r="283" spans="2:5">
       <c r="B283" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C283" t="str">
         <f t="shared" si="4"/>
@@ -7013,7 +7010,7 @@
     </row>
     <row r="284" spans="2:5">
       <c r="B284" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C284" t="str">
         <f t="shared" si="4"/>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="285" spans="2:5">
       <c r="B285" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C285" t="str">
         <f t="shared" si="4"/>
@@ -7043,7 +7040,7 @@
     </row>
     <row r="286" spans="2:5">
       <c r="B286" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C286" t="str">
         <f t="shared" si="4"/>
@@ -7058,7 +7055,7 @@
     </row>
     <row r="287" spans="2:5">
       <c r="B287" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C287" t="str">
         <f t="shared" si="4"/>
@@ -7073,7 +7070,7 @@
     </row>
     <row r="288" spans="2:5">
       <c r="B288" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C288" t="str">
         <f t="shared" si="4"/>
@@ -7088,7 +7085,7 @@
     </row>
     <row r="289" spans="2:5">
       <c r="B289" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C289" t="str">
         <f t="shared" si="4"/>
@@ -7103,7 +7100,7 @@
     </row>
     <row r="290" spans="2:5">
       <c r="B290" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C290" t="str">
         <f t="shared" si="4"/>
@@ -7118,7 +7115,7 @@
     </row>
     <row r="291" spans="2:5">
       <c r="B291" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C291" t="str">
         <f t="shared" si="4"/>
@@ -7133,7 +7130,7 @@
     </row>
     <row r="292" spans="2:5">
       <c r="B292" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C292" t="str">
         <f t="shared" si="4"/>
@@ -7148,7 +7145,7 @@
     </row>
     <row r="293" spans="2:5">
       <c r="B293" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C293" t="str">
         <f t="shared" si="4"/>
@@ -7163,7 +7160,7 @@
     </row>
     <row r="294" spans="2:5">
       <c r="B294" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C294" t="str">
         <f t="shared" si="4"/>
@@ -7178,7 +7175,7 @@
     </row>
     <row r="295" spans="2:5">
       <c r="B295" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C295" t="str">
         <f t="shared" si="4"/>
@@ -7193,7 +7190,7 @@
     </row>
     <row r="296" spans="2:5">
       <c r="B296" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C296" t="str">
         <f t="shared" si="4"/>
@@ -7208,7 +7205,7 @@
     </row>
     <row r="297" spans="2:5">
       <c r="B297" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C297" t="str">
         <f t="shared" si="4"/>
@@ -7223,7 +7220,7 @@
     </row>
     <row r="298" spans="2:5">
       <c r="B298" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C298" t="str">
         <f t="shared" si="4"/>
@@ -7238,7 +7235,7 @@
     </row>
     <row r="299" spans="2:5">
       <c r="B299" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C299" t="str">
         <f t="shared" si="4"/>
@@ -7253,7 +7250,7 @@
     </row>
     <row r="300" spans="2:5">
       <c r="B300" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C300" t="str">
         <f t="shared" si="4"/>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="301" spans="2:5">
       <c r="B301" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C301" t="str">
         <f t="shared" si="4"/>
@@ -7283,7 +7280,7 @@
     </row>
     <row r="302" spans="2:5">
       <c r="B302" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C302" t="str">
         <f t="shared" si="4"/>
@@ -7298,7 +7295,7 @@
     </row>
     <row r="303" spans="2:5">
       <c r="B303" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C303" t="str">
         <f t="shared" si="4"/>
@@ -7313,7 +7310,7 @@
     </row>
     <row r="304" spans="2:5">
       <c r="B304" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C304" t="str">
         <f t="shared" si="4"/>
@@ -7328,7 +7325,7 @@
     </row>
     <row r="305" spans="2:5">
       <c r="B305" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C305" t="str">
         <f t="shared" si="4"/>
@@ -7343,7 +7340,7 @@
     </row>
     <row r="306" spans="2:5">
       <c r="B306" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C306" t="str">
         <f t="shared" si="4"/>
@@ -7358,7 +7355,7 @@
     </row>
     <row r="307" spans="2:5">
       <c r="B307" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C307" t="str">
         <f t="shared" si="4"/>
@@ -7373,7 +7370,7 @@
     </row>
     <row r="308" spans="2:5">
       <c r="B308" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C308" t="str">
         <f t="shared" si="4"/>
@@ -7388,7 +7385,7 @@
     </row>
     <row r="309" spans="2:5">
       <c r="B309" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C309" t="str">
         <f t="shared" si="4"/>
@@ -7403,7 +7400,7 @@
     </row>
     <row r="310" spans="2:5">
       <c r="B310" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C310" t="str">
         <f t="shared" si="4"/>
@@ -7418,7 +7415,7 @@
     </row>
     <row r="311" spans="2:5">
       <c r="B311" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C311" t="str">
         <f t="shared" si="4"/>
@@ -7433,7 +7430,7 @@
     </row>
     <row r="312" spans="2:5">
       <c r="B312" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C312" t="str">
         <f t="shared" si="4"/>
@@ -7448,7 +7445,7 @@
     </row>
     <row r="313" spans="2:5">
       <c r="B313" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C313" t="str">
         <f t="shared" si="4"/>
@@ -7463,7 +7460,7 @@
     </row>
     <row r="314" spans="2:5">
       <c r="B314" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C314" t="str">
         <f t="shared" si="4"/>
@@ -7478,7 +7475,7 @@
     </row>
     <row r="315" spans="2:5">
       <c r="B315" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C315" t="str">
         <f t="shared" si="4"/>
@@ -7493,7 +7490,7 @@
     </row>
     <row r="316" spans="2:5">
       <c r="B316" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C316" t="str">
         <f t="shared" si="4"/>
@@ -7508,7 +7505,7 @@
     </row>
     <row r="317" spans="2:5">
       <c r="B317" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C317" t="str">
         <f t="shared" si="4"/>
@@ -7523,7 +7520,7 @@
     </row>
     <row r="318" spans="2:5">
       <c r="B318" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C318" t="str">
         <f t="shared" si="4"/>
@@ -7538,7 +7535,7 @@
     </row>
     <row r="319" spans="2:5">
       <c r="B319" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C319" t="str">
         <f t="shared" si="4"/>
@@ -7553,7 +7550,7 @@
     </row>
     <row r="320" spans="2:5">
       <c r="B320" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C320" t="str">
         <f t="shared" si="4"/>
@@ -7568,7 +7565,7 @@
     </row>
     <row r="321" spans="2:5">
       <c r="B321" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C321" t="str">
         <f t="shared" si="4"/>
@@ -7583,7 +7580,7 @@
     </row>
     <row r="322" spans="2:5">
       <c r="B322" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C322" t="str">
         <f t="shared" si="4"/>
@@ -7598,7 +7595,7 @@
     </row>
     <row r="323" spans="2:5">
       <c r="B323" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C323" t="str">
         <f t="shared" si="4"/>
@@ -7613,7 +7610,7 @@
     </row>
     <row r="324" spans="2:5">
       <c r="B324" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C324" t="str">
         <f t="shared" si="4"/>
